--- a/data/trans_camb/P32B-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P32B-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 3,34</t>
+          <t>-0,68; 3,53</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 3,82</t>
+          <t>-0,54; 3,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 7,54</t>
+          <t>1,05; 7,52</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,1</t>
+          <t>0,0; 2,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,09</t>
+          <t>0,0; 4,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,87</t>
+          <t>0,0; 4,36</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,61; 2,34</t>
+          <t>-0,36; 2,4</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,28; 3,03</t>
+          <t>-0,23; 3,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,09; 6,08</t>
+          <t>1,14; 6,26</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-43,85; 563,76</t>
+          <t>-49,4; 463,3</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-49,23; 635,54</t>
+          <t>-40,69; 533,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22,75; 1118,16</t>
+          <t>18,83; 1009,45</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-50,6; 485,37</t>
+          <t>-47,73; 445,34</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-38,44; 565,29</t>
+          <t>-32,39; 624,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>40,48; 1110,66</t>
+          <t>46,09; 1200,8</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,32; 3,54</t>
+          <t>1,3; 3,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,27</t>
+          <t>0,34; 2,24</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,24; 1,95</t>
+          <t>-0,25; 1,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 0,81</t>
+          <t>-1,79; 0,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,94</t>
+          <t>-1,6; 0,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 1,54</t>
+          <t>-1,68; 1,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,65; 2,34</t>
+          <t>0,67; 2,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,47</t>
+          <t>-0,03; 1,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 1,32</t>
+          <t>-0,43; 1,28</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>101,54; 1008,23</t>
+          <t>101,25; 941,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>24,46; 569,05</t>
+          <t>21,64; 631,11</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-38,96; 463,55</t>
+          <t>-33,19; 413,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-79,41; 138,33</t>
+          <t>-82,16; 154,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-76,22; 150,94</t>
+          <t>-75,99; 141,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-75,49; 205,77</t>
+          <t>-73,47; 197,57</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>42,84; 404,26</t>
+          <t>44,46; 365,0</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 252,58</t>
+          <t>-4,63; 254,66</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-36,41; 223,06</t>
+          <t>-35,6; 207,62</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,42; 5,0</t>
+          <t>0,45; 5,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,1; 3,62</t>
+          <t>0,12; 3,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 3,01</t>
+          <t>0,08; 3,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,7; 0,0</t>
+          <t>-3,61; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,55; 1,47</t>
+          <t>-2,14; 1,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 1,89</t>
+          <t>-1,78; 1,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,29; 2,68</t>
+          <t>-0,34; 2,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 2,33</t>
+          <t>-0,14; 2,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 2,19</t>
+          <t>-0,15; 2,25</t>
         </is>
       </c>
     </row>
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-84,21; —</t>
+          <t>-84,77; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-63,19; 1203,82</t>
+          <t>-57,41; 1451,09</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-38,71; 1097,01</t>
+          <t>-42,78; —</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-28,09; 1493,03</t>
+          <t>-52,56; 1077,21</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,99</t>
+          <t>1,25; 2,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,59; 2,14</t>
+          <t>0,55; 2,15</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,16</t>
+          <t>0,3; 2,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,4</t>
+          <t>-1,23; 0,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,83</t>
+          <t>-0,98; 0,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 1,27</t>
+          <t>-0,96; 1,34</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,61; 1,91</t>
+          <t>0,62; 1,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,47</t>
+          <t>0,22; 1,42</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,54</t>
+          <t>0,13; 1,48</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>97,1; 543,3</t>
+          <t>101,77; 512,95</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>47,49; 403,35</t>
+          <t>40,77; 373,62</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20,04; 369,91</t>
+          <t>19,66; 357,55</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-81,27; 79,7</t>
+          <t>-78,24; 100,15</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-63,54; 153,33</t>
+          <t>-63,88; 166,95</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-56,0; 181,71</t>
+          <t>-58,64; 220,69</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>47,67; 288,33</t>
+          <t>50,81; 307,45</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>20,65; 233,67</t>
+          <t>18,17; 233,56</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>7,75; 222,8</t>
+          <t>10,79; 226,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P32B-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P32B-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3,56</t>
+          <t>3,57</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,27</t>
+          <t>1,19</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>3,13</t>
+          <t>3,08</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 3,53</t>
+          <t>-0,65; 3,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 3,69</t>
+          <t>-0,37; 4,11</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,05; 7,52</t>
+          <t>1,2; 7,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,3</t>
+          <t>0,0; 2,46</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,08</t>
+          <t>0,0; 3,63</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,36</t>
+          <t>0,0; 4,11</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 2,4</t>
+          <t>-0,45; 2,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,23; 3,11</t>
+          <t>-0,33; 3,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,14; 6,26</t>
+          <t>0,92; 5,55</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>257,72%</t>
+          <t>258,13%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>306,82%</t>
+          <t>302,36%</t>
         </is>
       </c>
     </row>
@@ -783,17 +783,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-49,4; 463,3</t>
+          <t>-40,23; 586,91</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-40,69; 533,88</t>
+          <t>-36,21; 713,22</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18,83; 1009,45</t>
+          <t>34,91; 1334,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-47,73; 445,34</t>
+          <t>-44,32; 501,81</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,39; 624,45</t>
+          <t>-35,5; 584,67</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>46,09; 1200,8</t>
+          <t>23,27; 924,54</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>0,74</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,07</t>
+          <t>0,71</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,37</t>
+          <t>0,74</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,3; 3,54</t>
+          <t>1,36; 3,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,24</t>
+          <t>0,43; 2,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,81</t>
+          <t>-0,13; 1,87</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 0,89</t>
+          <t>-1,68; 0,89</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 0,86</t>
+          <t>-1,76; 0,8</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 1,53</t>
+          <t>-0,75; 2,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 2,3</t>
+          <t>0,65; 2,3</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,51</t>
+          <t>-0,05; 1,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-0,43; 1,28</t>
+          <t>-0,11; 1,74</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>105,57%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-5,04%</t>
+          <t>51,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>40,67%</t>
+          <t>79,81%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>101,25; 941,57</t>
+          <t>101,15; 830,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>21,64; 631,11</t>
+          <t>19,0; 538,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-33,19; 413,61</t>
+          <t>-31,12; 576,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-82,16; 154,82</t>
+          <t>-81,52; 147,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-75,99; 141,05</t>
+          <t>-78,29; 121,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-73,47; 197,57</t>
+          <t>-46,66; 416,01</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>44,46; 365,0</t>
+          <t>45,13; 383,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 254,66</t>
+          <t>-11,37; 228,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-35,6; 207,62</t>
+          <t>-16,78; 280,26</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1,38</t>
+          <t>1,94</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,68</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1,0</t>
+          <t>1,45</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,45; 5,19</t>
+          <t>0,57; 5,18</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,12; 3,84</t>
+          <t>0,3; 3,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 3,1</t>
+          <t>0,42; 3,95</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 0,0</t>
+          <t>-3,57; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,14; 1,68</t>
+          <t>-1,99; 1,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 1,94</t>
+          <t>-1,53; 2,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 2,71</t>
+          <t>-0,4; 2,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 2,38</t>
+          <t>-0,28; 2,38</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 2,25</t>
+          <t>0,22; 2,7</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>330,55%</t>
+          <t>462,6%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>154,31%</t>
+          <t>224,43%</t>
         </is>
       </c>
     </row>
@@ -1240,22 +1240,22 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-84,77; —</t>
+          <t>-85,41; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-57,41; 1451,09</t>
+          <t>-67,35; 1377,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-42,78; —</t>
+          <t>-49,72; 1043,63</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-52,56; 1077,21</t>
+          <t>-12,48; 1278,0</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,36</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,83</t>
+          <t>1,19</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,88</t>
+          <t>1,22; 3,1</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,15</t>
+          <t>0,56; 2,16</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,11</t>
+          <t>0,53; 2,32</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,44</t>
+          <t>-1,33; 0,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,83</t>
+          <t>-1,04; 0,9</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 1,34</t>
+          <t>-0,16; 2,17</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,93</t>
+          <t>0,56; 1,95</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,22; 1,42</t>
+          <t>0,29; 1,4</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,48</t>
+          <t>0,56; 1,98</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>141,3%</t>
+          <t>166,75%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>133,91%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>101,77; 512,95</t>
+          <t>92,88; 617,14</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>40,77; 373,62</t>
+          <t>43,81; 418,43</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19,66; 357,55</t>
+          <t>38,56; 456,4</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-78,24; 100,15</t>
+          <t>-79,42; 105,04</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-63,88; 166,95</t>
+          <t>-62,17; 158,79</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-58,64; 220,69</t>
+          <t>-18,37; 375,11</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>50,81; 307,45</t>
+          <t>43,16; 287,74</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>18,17; 233,56</t>
+          <t>20,67; 219,8</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>10,79; 226,85</t>
+          <t>40,77; 304,22</t>
         </is>
       </c>
     </row>
